--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/11.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/11.xlsx
@@ -426,13 +426,13 @@
         <v>-9.304834989435083</v>
       </c>
       <c r="E2">
-        <v>-11.78902827408993</v>
+        <v>-16.02045702922715</v>
       </c>
       <c r="F2">
-        <v>-2.096607155774487</v>
+        <v>-2.111973371096418</v>
       </c>
       <c r="G2">
-        <v>-5.434331174838312</v>
+        <v>-7.660073841255578</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.72084048066611</v>
       </c>
       <c r="E3">
-        <v>-12.79972027396584</v>
+        <v>-17.67251680280942</v>
       </c>
       <c r="F3">
-        <v>-2.15512468584305</v>
+        <v>-1.69801001542581</v>
       </c>
       <c r="G3">
-        <v>-5.193462502492019</v>
+        <v>-7.579491852284177</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.12202952624543</v>
       </c>
       <c r="E4">
-        <v>-13.16592891001813</v>
+        <v>-18.41990973845736</v>
       </c>
       <c r="F4">
-        <v>-1.804849529569279</v>
+        <v>-1.900841572573089</v>
       </c>
       <c r="G4">
-        <v>-5.938437875739754</v>
+        <v>-7.312383795993621</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.45153953207246</v>
       </c>
       <c r="E5">
-        <v>-14.02658350907191</v>
+        <v>-18.7572810520288</v>
       </c>
       <c r="F5">
-        <v>-1.394938547233166</v>
+        <v>-1.657101091238556</v>
       </c>
       <c r="G5">
-        <v>-5.967196584839402</v>
+        <v>-6.62376052891536</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.70034201170651</v>
       </c>
       <c r="E6">
-        <v>-13.89887148510759</v>
+        <v>-18.99870758679973</v>
       </c>
       <c r="F6">
-        <v>-1.597469407013228</v>
+        <v>-2.03130032647258</v>
       </c>
       <c r="G6">
-        <v>-6.258488176294335</v>
+        <v>-7.548068154025415</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.8540029134213</v>
       </c>
       <c r="E7">
-        <v>-15.10037979424472</v>
+        <v>-19.94528998014906</v>
       </c>
       <c r="F7">
-        <v>-1.163263237120409</v>
+        <v>-1.854385900256689</v>
       </c>
       <c r="G7">
-        <v>-5.833049969042595</v>
+        <v>-6.405357218598562</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.91055901470573</v>
       </c>
       <c r="E8">
-        <v>-16.45331574572433</v>
+        <v>-20.31201033376421</v>
       </c>
       <c r="F8">
-        <v>-1.240204486594635</v>
+        <v>-1.522667830540433</v>
       </c>
       <c r="G8">
-        <v>-5.334690375197328</v>
+        <v>-6.954874672662186</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.85323377231555</v>
       </c>
       <c r="E9">
-        <v>-17.14960938066971</v>
+        <v>-20.20810449765821</v>
       </c>
       <c r="F9">
-        <v>-1.474090709305464</v>
+        <v>-1.977631230812603</v>
       </c>
       <c r="G9">
-        <v>-5.533438976647473</v>
+        <v>-6.328526077723156</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.67787082370529</v>
       </c>
       <c r="E10">
-        <v>-16.38922425309377</v>
+        <v>-20.38233300662932</v>
       </c>
       <c r="F10">
-        <v>-1.182149185536835</v>
+        <v>-1.809534775599513</v>
       </c>
       <c r="G10">
-        <v>-5.564882538179472</v>
+        <v>-6.802930564046257</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.38455437717242</v>
       </c>
       <c r="E11">
-        <v>-18.17945682559808</v>
+        <v>-22.26620989313824</v>
       </c>
       <c r="F11">
-        <v>-0.8815329983260884</v>
+        <v>-1.569589045337205</v>
       </c>
       <c r="G11">
-        <v>-4.469379982142625</v>
+        <v>-6.586748629786308</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.967728501068184</v>
       </c>
       <c r="E12">
-        <v>-19.69261018746906</v>
+        <v>-23.86289095808071</v>
       </c>
       <c r="F12">
-        <v>-0.670495633686678</v>
+        <v>-1.247217445026736</v>
       </c>
       <c r="G12">
-        <v>-4.404821033581298</v>
+        <v>-5.742781323823287</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.423728759262236</v>
       </c>
       <c r="E13">
-        <v>-19.47879828719691</v>
+        <v>-22.10440751684418</v>
       </c>
       <c r="F13">
-        <v>-1.159735220351886</v>
+        <v>-1.262852051387174</v>
       </c>
       <c r="G13">
-        <v>-4.102733753122802</v>
+        <v>-5.586232246362231</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.766213092132888</v>
       </c>
       <c r="E14">
-        <v>-20.65290027163961</v>
+        <v>-24.39083404331695</v>
       </c>
       <c r="F14">
-        <v>-0.5157433489652855</v>
+        <v>-1.053809395453704</v>
       </c>
       <c r="G14">
-        <v>-3.136915197495826</v>
+        <v>-5.781100888440351</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.004047392917368</v>
       </c>
       <c r="E15">
-        <v>-21.57686746579463</v>
+        <v>-25.23571596740201</v>
       </c>
       <c r="F15">
-        <v>-0.7140776994827656</v>
+        <v>-1.131820895612348</v>
       </c>
       <c r="G15">
-        <v>-3.091282637782512</v>
+        <v>-4.531558648461217</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.147720188837802</v>
       </c>
       <c r="E16">
-        <v>-21.94640905871656</v>
+        <v>-26.62624278161929</v>
       </c>
       <c r="F16">
-        <v>-0.1773478096150623</v>
+        <v>-0.4288964820883826</v>
       </c>
       <c r="G16">
-        <v>-2.465407450855598</v>
+        <v>-4.081109269660282</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.225324963953266</v>
       </c>
       <c r="E17">
-        <v>-22.88956792571609</v>
+        <v>-26.51312150090769</v>
       </c>
       <c r="F17">
-        <v>-0.2720194349788094</v>
+        <v>-0.3810764886595727</v>
       </c>
       <c r="G17">
-        <v>-1.754126810106565</v>
+        <v>-4.149227054676326</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.262860296196573</v>
       </c>
       <c r="E18">
-        <v>-22.97864753792097</v>
+        <v>-28.76140921928785</v>
       </c>
       <c r="F18">
-        <v>0.08453723131039019</v>
+        <v>-0.3025613411200272</v>
       </c>
       <c r="G18">
-        <v>-1.897466810865929</v>
+        <v>-4.454717575949193</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.284156532638412</v>
       </c>
       <c r="E19">
-        <v>-24.03556620046719</v>
+        <v>-28.31496055229366</v>
       </c>
       <c r="F19">
-        <v>-0.3940628044332606</v>
+        <v>-0.1787419519539739</v>
       </c>
       <c r="G19">
-        <v>-0.4080920992942931</v>
+        <v>-3.487551628287734</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.325935130432254</v>
       </c>
       <c r="E20">
-        <v>-25.78141067074831</v>
+        <v>-27.87319432742339</v>
       </c>
       <c r="F20">
-        <v>0.3206832402960564</v>
+        <v>0.1982919565324295</v>
       </c>
       <c r="G20">
-        <v>-0.07021451101073652</v>
+        <v>-3.177535591262683</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.420193822798389</v>
       </c>
       <c r="E21">
-        <v>-25.31220642186557</v>
+        <v>-28.83155075319266</v>
       </c>
       <c r="F21">
-        <v>0.603990690625307</v>
+        <v>0.01936128405812509</v>
       </c>
       <c r="G21">
-        <v>-0.05715771940385096</v>
+        <v>-3.210200744098672</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.589883112719315</v>
       </c>
       <c r="E22">
-        <v>-25.83907173028798</v>
+        <v>-29.49908857818934</v>
       </c>
       <c r="F22">
-        <v>0.8581694296025156</v>
+        <v>0.4448306629536183</v>
       </c>
       <c r="G22">
-        <v>0.1941557241188427</v>
+        <v>-2.18140568067814</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.8619802831705879</v>
       </c>
       <c r="E23">
-        <v>-26.9370274242917</v>
+        <v>-30.99732967515307</v>
       </c>
       <c r="F23">
-        <v>1.215656352485059</v>
+        <v>0.03903086803759935</v>
       </c>
       <c r="G23">
-        <v>0.276035446941637</v>
+        <v>-2.354080425460986</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.2573960872650176</v>
       </c>
       <c r="E24">
-        <v>-26.938974668115</v>
+        <v>-30.71673410445279</v>
       </c>
       <c r="F24">
-        <v>1.761648218283464</v>
+        <v>0.2180493474566005</v>
       </c>
       <c r="G24">
-        <v>2.11904594356376</v>
+        <v>-2.829335721987679</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.2156218709196887</v>
       </c>
       <c r="E25">
-        <v>-27.9289353139838</v>
+        <v>-32.70943701407705</v>
       </c>
       <c r="F25">
-        <v>1.255530645786216</v>
+        <v>0.491300417515865</v>
       </c>
       <c r="G25">
-        <v>1.080309311888797</v>
+        <v>-1.525861384628277</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.5502128968724641</v>
       </c>
       <c r="E26">
-        <v>-27.98417363992937</v>
+        <v>-31.58831817552409</v>
       </c>
       <c r="F26">
-        <v>1.249410667414333</v>
+        <v>0.7659688242013195</v>
       </c>
       <c r="G26">
-        <v>0.1530950277952621</v>
+        <v>-1.226717179154194</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.7443328205970406</v>
       </c>
       <c r="E27">
-        <v>-29.03261499913322</v>
+        <v>-30.8536502518377</v>
       </c>
       <c r="F27">
-        <v>1.391487274138088</v>
+        <v>0.9454130844653597</v>
       </c>
       <c r="G27">
-        <v>1.256006584748997</v>
+        <v>-2.307659955909325</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.8086631686676631</v>
       </c>
       <c r="E28">
-        <v>-28.17327365754166</v>
+        <v>-31.16869845278833</v>
       </c>
       <c r="F28">
-        <v>1.920746118399942</v>
+        <v>0.6800671245310108</v>
       </c>
       <c r="G28">
-        <v>0.4623165338908873</v>
+        <v>-1.523414891474756</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.7556998630837207</v>
       </c>
       <c r="E29">
-        <v>-29.19703936187772</v>
+        <v>-30.86341364179824</v>
       </c>
       <c r="F29">
-        <v>1.676999010126188</v>
+        <v>0.876070449177013</v>
       </c>
       <c r="G29">
-        <v>1.301659007735547</v>
+        <v>-2.117512151770206</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.599188047608526</v>
       </c>
       <c r="E30">
-        <v>-28.20800252470649</v>
+        <v>-31.53622940325086</v>
       </c>
       <c r="F30">
-        <v>1.142103954055685</v>
+        <v>0.8701741300038861</v>
       </c>
       <c r="G30">
-        <v>-0.106587474850709</v>
+        <v>-2.727367608832587</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.361717452490493</v>
       </c>
       <c r="E31">
-        <v>-28.60438891154589</v>
+        <v>-32.16021462947877</v>
       </c>
       <c r="F31">
-        <v>1.495323128079006</v>
+        <v>0.6858855771682745</v>
       </c>
       <c r="G31">
-        <v>0.9539524097458942</v>
+        <v>-1.788271776798608</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.06439969833478863</v>
       </c>
       <c r="E32">
-        <v>-27.0183814598395</v>
+        <v>-31.65914350900405</v>
       </c>
       <c r="F32">
-        <v>1.499819506341401</v>
+        <v>1.089996330949985</v>
       </c>
       <c r="G32">
-        <v>-0.002321843091363016</v>
+        <v>-1.297648927878618</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.2735188986117032</v>
       </c>
       <c r="E33">
-        <v>-27.95138295963983</v>
+        <v>-30.59495438143852</v>
       </c>
       <c r="F33">
-        <v>1.438001760540086</v>
+        <v>0.8574437797576633</v>
       </c>
       <c r="G33">
-        <v>-0.08453593101362368</v>
+        <v>-1.585752463979232</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.6286662340312393</v>
       </c>
       <c r="E34">
-        <v>-27.97072407212659</v>
+        <v>-30.78857608034748</v>
       </c>
       <c r="F34">
-        <v>1.317528975681342</v>
+        <v>0.572057127247386</v>
       </c>
       <c r="G34">
-        <v>0.3759179164069879</v>
+        <v>-1.846673110656891</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9833770904099376</v>
       </c>
       <c r="E35">
-        <v>-27.06915923888751</v>
+        <v>-30.42556454694461</v>
       </c>
       <c r="F35">
-        <v>1.343857805211922</v>
+        <v>0.5797427200105598</v>
       </c>
       <c r="G35">
-        <v>0.395268055084028</v>
+        <v>-2.435655578094167</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.321957912366991</v>
       </c>
       <c r="E36">
-        <v>-25.49109925906458</v>
+        <v>-30.23745173666598</v>
       </c>
       <c r="F36">
-        <v>1.475157352025255</v>
+        <v>0.7824102604120841</v>
       </c>
       <c r="G36">
-        <v>0.1822907289060947</v>
+        <v>-2.441008730231169</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.629896175106608</v>
       </c>
       <c r="E37">
-        <v>-25.92536180250414</v>
+        <v>-28.11717945000865</v>
       </c>
       <c r="F37">
-        <v>1.410687173800175</v>
+        <v>0.4994954562317606</v>
       </c>
       <c r="G37">
-        <v>0.2990669122583466</v>
+        <v>-2.804827753360454</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.89903991047531</v>
       </c>
       <c r="E38">
-        <v>-24.47285829301788</v>
+        <v>-29.33544311297415</v>
       </c>
       <c r="F38">
-        <v>1.745672324553072</v>
+        <v>0.02999089457084835</v>
       </c>
       <c r="G38">
-        <v>-0.3578280863715387</v>
+        <v>-2.53589227593222</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.12389284966639</v>
       </c>
       <c r="E39">
-        <v>-24.51677996241827</v>
+        <v>-28.11459369135027</v>
       </c>
       <c r="F39">
-        <v>1.163513937948441</v>
+        <v>0.6746512584515076</v>
       </c>
       <c r="G39">
-        <v>-1.263742320465403</v>
+        <v>-3.218407586490525</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.300549490910295</v>
       </c>
       <c r="E40">
-        <v>-24.85271574972928</v>
+        <v>-28.30585379106423</v>
       </c>
       <c r="F40">
-        <v>1.287994364301929</v>
+        <v>0.4507418927399957</v>
       </c>
       <c r="G40">
-        <v>-0.8546350343588872</v>
+        <v>-2.17958819117708</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.43006570957039</v>
       </c>
       <c r="E41">
-        <v>-23.69731183446425</v>
+        <v>-28.69970423245934</v>
       </c>
       <c r="F41">
-        <v>1.477347555438256</v>
+        <v>0.07580458215007781</v>
       </c>
       <c r="G41">
-        <v>-0.7512599393496051</v>
+        <v>-3.075656862837152</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.517906189979914</v>
       </c>
       <c r="E42">
-        <v>-22.28349507842552</v>
+        <v>-27.31314888994678</v>
       </c>
       <c r="F42">
-        <v>1.657033698983914</v>
+        <v>0.2931963531363633</v>
       </c>
       <c r="G42">
-        <v>-0.594316906969376</v>
+        <v>-3.691560686599781</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.570384494550188</v>
       </c>
       <c r="E43">
-        <v>-20.59503090229559</v>
+        <v>-23.79272225333186</v>
       </c>
       <c r="F43">
-        <v>1.894299660698165</v>
+        <v>0.2896393435087422</v>
       </c>
       <c r="G43">
-        <v>-1.961797331785047</v>
+        <v>-2.849526739231694</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.596123297201485</v>
       </c>
       <c r="E44">
-        <v>-20.84868884536124</v>
+        <v>-24.35686595978541</v>
       </c>
       <c r="F44">
-        <v>0.8109243231512486</v>
+        <v>0.512103208102369</v>
       </c>
       <c r="G44">
-        <v>-1.069873463140143</v>
+        <v>-2.347449402745826</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.608806107471834</v>
       </c>
       <c r="E45">
-        <v>-20.125323992798</v>
+        <v>-24.5789649674916</v>
       </c>
       <c r="F45">
-        <v>1.845553552513026</v>
+        <v>0.835208741931719</v>
       </c>
       <c r="G45">
-        <v>-1.249089845908588</v>
+        <v>-2.432732366382991</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.622008288644904</v>
       </c>
       <c r="E46">
-        <v>-19.79071504837124</v>
+        <v>-23.71794809051721</v>
       </c>
       <c r="F46">
-        <v>1.584016425896749</v>
+        <v>0.7186375675401614</v>
       </c>
       <c r="G46">
-        <v>-1.933657694701242</v>
+        <v>-2.166898870125054</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.647402696064361</v>
       </c>
       <c r="E47">
-        <v>-19.50986814736353</v>
+        <v>-23.8821279156653</v>
       </c>
       <c r="F47">
-        <v>1.641685707744845</v>
+        <v>0.5104224506420888</v>
       </c>
       <c r="G47">
-        <v>-1.394863097639317</v>
+        <v>-3.221658542210089</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.702625334261209</v>
       </c>
       <c r="E48">
-        <v>-18.63583643609109</v>
+        <v>-22.6150427744231</v>
       </c>
       <c r="F48">
-        <v>1.681321431233996</v>
+        <v>0.9202042076633651</v>
       </c>
       <c r="G48">
-        <v>-2.000004337853775</v>
+        <v>-3.336974774979523</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.803217089668465</v>
       </c>
       <c r="E49">
-        <v>-17.45594253339258</v>
+        <v>-21.23785231615841</v>
       </c>
       <c r="F49">
-        <v>1.718780205188589</v>
+        <v>1.282782276603514</v>
       </c>
       <c r="G49">
-        <v>-1.852440080986302</v>
+        <v>-2.80861832800292</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.956744647882941</v>
       </c>
       <c r="E50">
-        <v>-17.35975774546966</v>
+        <v>-21.45274652171839</v>
       </c>
       <c r="F50">
-        <v>1.518833851705261</v>
+        <v>0.4788483987169829</v>
       </c>
       <c r="G50">
-        <v>-1.890994694336654</v>
+        <v>-3.667913459812767</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.176633144594635</v>
       </c>
       <c r="E51">
-        <v>-16.72602045046624</v>
+        <v>-20.27799243701859</v>
       </c>
       <c r="F51">
-        <v>1.32299951400943</v>
+        <v>0.497741802440034</v>
       </c>
       <c r="G51">
-        <v>-0.9826405881803469</v>
+        <v>-3.704498298567253</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.472682658815258</v>
       </c>
       <c r="E52">
-        <v>-15.93518133518871</v>
+        <v>-20.09896827407336</v>
       </c>
       <c r="F52">
-        <v>2.320436703720315</v>
+        <v>0.8161016194187456</v>
       </c>
       <c r="G52">
-        <v>-2.603655832575562</v>
+        <v>-2.859153805659894</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.83997884353063</v>
       </c>
       <c r="E53">
-        <v>-16.0527224065318</v>
+        <v>-19.34104663635758</v>
       </c>
       <c r="F53">
-        <v>2.028973976310503</v>
+        <v>0.8971408024346212</v>
       </c>
       <c r="G53">
-        <v>-2.312847580769363</v>
+        <v>-3.743741505389774</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.27991186123533</v>
       </c>
       <c r="E54">
-        <v>-14.52599267958582</v>
+        <v>-18.28657787824952</v>
       </c>
       <c r="F54">
-        <v>1.669643107589328</v>
+        <v>0.9425022014119221</v>
       </c>
       <c r="G54">
-        <v>-2.804089501705197</v>
+        <v>-3.448824866569339</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.789147281563989</v>
       </c>
       <c r="E55">
-        <v>-13.27614743889082</v>
+        <v>-17.945031311643</v>
       </c>
       <c r="F55">
-        <v>1.861042366210571</v>
+        <v>1.417854208569196</v>
       </c>
       <c r="G55">
-        <v>-3.090074288660678</v>
+        <v>-3.615990863574838</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.34855492541688</v>
       </c>
       <c r="E56">
-        <v>-13.58173339340242</v>
+        <v>-17.69729661257939</v>
       </c>
       <c r="F56">
-        <v>1.885724401344385</v>
+        <v>0.6991676201047617</v>
       </c>
       <c r="G56">
-        <v>-2.189533069977051</v>
+        <v>-4.522315605315572</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.943740978732253</v>
       </c>
       <c r="E57">
-        <v>-12.46255727019876</v>
+        <v>-16.93241471031383</v>
       </c>
       <c r="F57">
-        <v>1.370042498814414</v>
+        <v>1.069949839802237</v>
       </c>
       <c r="G57">
-        <v>-3.064457287277797</v>
+        <v>-4.799984301876403</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.559405013932374</v>
       </c>
       <c r="E58">
-        <v>-10.71202582931969</v>
+        <v>-16.90344606208676</v>
       </c>
       <c r="F58">
-        <v>1.581234768158148</v>
+        <v>0.9007491708412159</v>
       </c>
       <c r="G58">
-        <v>-3.662712592770572</v>
+        <v>-4.818625983808039</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.16877950563533</v>
       </c>
       <c r="E59">
-        <v>-11.99501949975084</v>
+        <v>-16.77260939105715</v>
       </c>
       <c r="F59">
-        <v>1.515909714773379</v>
+        <v>0.8468058855709121</v>
       </c>
       <c r="G59">
-        <v>-3.74348659338325</v>
+        <v>-5.319087774070743</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.749105312476789</v>
       </c>
       <c r="E60">
-        <v>-10.90285119552892</v>
+        <v>-15.52461176775728</v>
       </c>
       <c r="F60">
-        <v>1.147062561328843</v>
+        <v>0.5141658429353397</v>
       </c>
       <c r="G60">
-        <v>-4.471485489105602</v>
+        <v>-4.43047445096511</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.284539747527406</v>
       </c>
       <c r="E61">
-        <v>-10.61578217123468</v>
+        <v>-14.94843590586535</v>
       </c>
       <c r="F61">
-        <v>1.61040489788033</v>
+        <v>0.9643860114590794</v>
       </c>
       <c r="G61">
-        <v>-3.353865178320885</v>
+        <v>-5.626766565945068</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.754503132472246</v>
       </c>
       <c r="E62">
-        <v>-10.79210736367134</v>
+        <v>-16.27703583802774</v>
       </c>
       <c r="F62">
-        <v>1.312257245529926</v>
+        <v>0.3165960755306437</v>
       </c>
       <c r="G62">
-        <v>-4.374274629890443</v>
+        <v>-5.596418794986569</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.141893392010482</v>
       </c>
       <c r="E63">
-        <v>-9.345649366985317</v>
+        <v>-14.60236086525117</v>
       </c>
       <c r="F63">
-        <v>0.9920717067954445</v>
+        <v>0.7064100363074378</v>
       </c>
       <c r="G63">
-        <v>-3.725275282371719</v>
+        <v>-4.614044201117697</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.441843094088464</v>
       </c>
       <c r="E64">
-        <v>-9.80896207118408</v>
+        <v>-15.83744328068116</v>
       </c>
       <c r="F64">
-        <v>0.8890377125004365</v>
+        <v>0.6165653077998035</v>
       </c>
       <c r="G64">
-        <v>-3.824191072539603</v>
+        <v>-5.405764477379941</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.648941582813395</v>
       </c>
       <c r="E65">
-        <v>-9.181039336806499</v>
+        <v>-15.66066071236972</v>
       </c>
       <c r="F65">
-        <v>1.133961102486166</v>
+        <v>0.1434623181411302</v>
       </c>
       <c r="G65">
-        <v>-3.462715915652121</v>
+        <v>-5.412243215000295</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.757325336338923</v>
       </c>
       <c r="E66">
-        <v>-9.620890017171522</v>
+        <v>-14.59991548928703</v>
       </c>
       <c r="F66">
-        <v>0.4419578848007097</v>
+        <v>0.2013544308205793</v>
       </c>
       <c r="G66">
-        <v>-3.928870522491358</v>
+        <v>-5.854479130318297</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.772597768269224</v>
       </c>
       <c r="E67">
-        <v>-9.519366158393559</v>
+        <v>-13.70439164037418</v>
       </c>
       <c r="F67">
-        <v>0.4063529970935813</v>
+        <v>-0.1500564171624298</v>
       </c>
       <c r="G67">
-        <v>-3.996339440581704</v>
+        <v>-5.110884254560439</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.701071678313774</v>
       </c>
       <c r="E68">
-        <v>-9.162794115029596</v>
+        <v>-14.49158080560153</v>
       </c>
       <c r="F68">
-        <v>0.1500321000127331</v>
+        <v>0.1804422957369058</v>
       </c>
       <c r="G68">
-        <v>-3.735332719720025</v>
+        <v>-6.557473475582533</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.543704853666027</v>
       </c>
       <c r="E69">
-        <v>-7.882716781859394</v>
+        <v>-13.54897894090494</v>
       </c>
       <c r="F69">
-        <v>0.2327570106933057</v>
+        <v>-0.2226711036918345</v>
       </c>
       <c r="G69">
-        <v>-4.649298200565396</v>
+        <v>-5.136607193400576</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.308434085487498</v>
       </c>
       <c r="E70">
-        <v>-8.43965568616674</v>
+        <v>-15.56070370559842</v>
       </c>
       <c r="F70">
-        <v>-0.204981317805051</v>
+        <v>-0.01060904857516102</v>
       </c>
       <c r="G70">
-        <v>-3.410783387777574</v>
+        <v>-4.640992041807364</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.006685578887454</v>
       </c>
       <c r="E71">
-        <v>-9.538594059030128</v>
+        <v>-13.77019036770563</v>
       </c>
       <c r="F71">
-        <v>-0.02587751654356151</v>
+        <v>-0.1877868956251417</v>
       </c>
       <c r="G71">
-        <v>-2.925891093186062</v>
+        <v>-4.834298106390949</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.640833011224171</v>
       </c>
       <c r="E72">
-        <v>-8.460971213320844</v>
+        <v>-13.77197911493866</v>
       </c>
       <c r="F72">
-        <v>-0.02140764603805538</v>
+        <v>-0.5071589775700742</v>
       </c>
       <c r="G72">
-        <v>-3.361125204688506</v>
+        <v>-5.161581948948838</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.214146908695733</v>
       </c>
       <c r="E73">
-        <v>-9.360996365397313</v>
+        <v>-14.67516967034649</v>
       </c>
       <c r="F73">
-        <v>-0.5579014511959608</v>
+        <v>-0.3020957986396539</v>
       </c>
       <c r="G73">
-        <v>-2.613498084463815</v>
+        <v>-4.782944923985774</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.739481290877999</v>
       </c>
       <c r="E74">
-        <v>-8.083749328481904</v>
+        <v>-14.38111773913242</v>
       </c>
       <c r="F74">
-        <v>-0.05710282579208887</v>
+        <v>-0.7225079945410562</v>
       </c>
       <c r="G74">
-        <v>-2.184554009485987</v>
+        <v>-3.88071201653158</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.219255829630092</v>
       </c>
       <c r="E75">
-        <v>-9.896352562584102</v>
+        <v>-15.00584337086059</v>
       </c>
       <c r="F75">
-        <v>-0.3839376696688422</v>
+        <v>-0.5689634694929454</v>
       </c>
       <c r="G75">
-        <v>-2.97027888777661</v>
+        <v>-4.056505295212419</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.65386436790249</v>
       </c>
       <c r="E76">
-        <v>-7.984458007389723</v>
+        <v>-15.26215047122072</v>
       </c>
       <c r="F76">
-        <v>-0.7748956058289025</v>
+        <v>-0.950524405835648</v>
       </c>
       <c r="G76">
-        <v>-2.393578544290031</v>
+        <v>-4.432907701936474</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.055808248736992</v>
       </c>
       <c r="E77">
-        <v>-10.35429902508377</v>
+        <v>-16.36898197427948</v>
       </c>
       <c r="F77">
-        <v>-0.7014127902613639</v>
+        <v>-0.7594962558108597</v>
       </c>
       <c r="G77">
-        <v>-1.516932843308863</v>
+        <v>-4.782776086163271</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.430472598421273</v>
       </c>
       <c r="E78">
-        <v>-10.20980447644703</v>
+        <v>-16.14034837858022</v>
       </c>
       <c r="F78">
-        <v>-0.7889488588173961</v>
+        <v>-1.014083379917649</v>
       </c>
       <c r="G78">
-        <v>-0.6519468837170088</v>
+        <v>-2.938838636790152</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.780433809339256</v>
       </c>
       <c r="E79">
-        <v>-9.66591210575578</v>
+        <v>-16.90237281374694</v>
       </c>
       <c r="F79">
-        <v>-1.280406813387301</v>
+        <v>-0.9265357142179772</v>
       </c>
       <c r="G79">
-        <v>-0.6824270764970786</v>
+        <v>-3.509907742314432</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.120465241722574</v>
       </c>
       <c r="E80">
-        <v>-10.75746000903865</v>
+        <v>-16.75042439689357</v>
       </c>
       <c r="F80">
-        <v>-1.038994044454635</v>
+        <v>-0.6730171840607997</v>
       </c>
       <c r="G80">
-        <v>-0.8938616884537115</v>
+        <v>-2.979488825466863</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.462082554043596</v>
       </c>
       <c r="E81">
-        <v>-11.6170911729667</v>
+        <v>-17.43507985363924</v>
       </c>
       <c r="F81">
-        <v>-0.6621929072084185</v>
+        <v>-0.9361282087423954</v>
       </c>
       <c r="G81">
-        <v>-0.1314264980318608</v>
+        <v>-3.006880279258793</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.813083091216961</v>
       </c>
       <c r="E82">
-        <v>-12.29386255646502</v>
+        <v>-19.01548105452414</v>
       </c>
       <c r="F82">
-        <v>-0.8347733151728619</v>
+        <v>-1.418892447419919</v>
       </c>
       <c r="G82">
-        <v>0.7481755201158758</v>
+        <v>-2.044557659721287</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.190285838070612</v>
       </c>
       <c r="E83">
-        <v>-12.98313705669852</v>
+        <v>-19.04277416736837</v>
       </c>
       <c r="F83">
-        <v>-0.5286766492251942</v>
+        <v>-1.385386642711485</v>
       </c>
       <c r="G83">
-        <v>0.6671234336778994</v>
+        <v>-2.188715365228851</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.610179972941495</v>
       </c>
       <c r="E84">
-        <v>-13.54349948735566</v>
+        <v>-21.10426233293213</v>
       </c>
       <c r="F84">
-        <v>-0.3864161449380183</v>
+        <v>-1.330834507400124</v>
       </c>
       <c r="G84">
-        <v>0.8114036293704162</v>
+        <v>-1.927377589813244</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.084171927306897</v>
       </c>
       <c r="E85">
-        <v>-15.05285345953422</v>
+        <v>-21.41477073869007</v>
       </c>
       <c r="F85">
-        <v>-0.9068338239097937</v>
+        <v>-1.262722826072337</v>
       </c>
       <c r="G85">
-        <v>1.470771605518137</v>
+        <v>-1.463686028855225</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.6286073344659063</v>
       </c>
       <c r="E86">
-        <v>-17.04961161763234</v>
+        <v>-22.28089573434512</v>
       </c>
       <c r="F86">
-        <v>-1.215005550201474</v>
+        <v>-1.063510406107889</v>
       </c>
       <c r="G86">
-        <v>1.554581376390326</v>
+        <v>-1.402954070937295</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.2600963692381875</v>
       </c>
       <c r="E87">
-        <v>-17.74538900654085</v>
+        <v>-22.10637287456351</v>
       </c>
       <c r="F87">
-        <v>-1.16689148634467</v>
+        <v>-1.415748793126295</v>
       </c>
       <c r="G87">
-        <v>2.122694164748037</v>
+        <v>-1.741877791611262</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.01281811490194502</v>
       </c>
       <c r="E88">
-        <v>-18.66408505695094</v>
+        <v>-24.34164123017162</v>
       </c>
       <c r="F88">
-        <v>-0.8269369595423787</v>
+        <v>-1.739248629839378</v>
       </c>
       <c r="G88">
-        <v>2.179466710200999</v>
+        <v>-0.2338415348347542</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.1793433630506983</v>
       </c>
       <c r="E89">
-        <v>-20.0563689190832</v>
+        <v>-25.57107663851405</v>
       </c>
       <c r="F89">
-        <v>-1.299228149146308</v>
+        <v>-1.548652887598851</v>
       </c>
       <c r="G89">
-        <v>1.55320418944599</v>
+        <v>-0.4017126780401176</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.2289323654748922</v>
       </c>
       <c r="E90">
-        <v>-22.69638322454887</v>
+        <v>-26.20468260777125</v>
       </c>
       <c r="F90">
-        <v>-0.8302877056867026</v>
+        <v>-1.642933523548476</v>
       </c>
       <c r="G90">
-        <v>1.448514807857617</v>
+        <v>-0.01386240484126237</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.1622980665535428</v>
       </c>
       <c r="E91">
-        <v>-24.02947540292687</v>
+        <v>-28.09233624160257</v>
       </c>
       <c r="F91">
-        <v>-1.295193171527272</v>
+        <v>-1.870627699923379</v>
       </c>
       <c r="G91">
-        <v>2.149317571974856</v>
+        <v>-0.5896026901214538</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.02290875006740719</v>
       </c>
       <c r="E92">
-        <v>-25.14890964914898</v>
+        <v>-29.92693880243403</v>
       </c>
       <c r="F92">
-        <v>-1.158527460678604</v>
+        <v>-2.423205914941443</v>
       </c>
       <c r="G92">
-        <v>2.071817700900517</v>
+        <v>-1.484522602479398</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.3279403091445251</v>
       </c>
       <c r="E93">
-        <v>-26.96154458256923</v>
+        <v>-33.32023079552062</v>
       </c>
       <c r="F93">
-        <v>-1.200236587776962</v>
+        <v>-2.197136995410832</v>
       </c>
       <c r="G93">
-        <v>1.63996034584813</v>
+        <v>-0.29064056465203</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.7409959081354616</v>
       </c>
       <c r="E94">
-        <v>-30.05045293099324</v>
+        <v>-33.61669413914377</v>
       </c>
       <c r="F94">
-        <v>-1.28406985404248</v>
+        <v>-1.795093846666509</v>
       </c>
       <c r="G94">
-        <v>1.224251831936308</v>
+        <v>0.0487830483983663</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.252767531573979</v>
       </c>
       <c r="E95">
-        <v>-31.96290901696457</v>
+        <v>-35.45013061791825</v>
       </c>
       <c r="F95">
-        <v>-1.321304968798318</v>
+        <v>-1.787390858187877</v>
       </c>
       <c r="G95">
-        <v>0.5373632907206259</v>
+        <v>-2.174933564148865</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.857494318354957</v>
       </c>
       <c r="E96">
-        <v>-33.52108899589383</v>
+        <v>-38.0166840180315</v>
       </c>
       <c r="F96">
-        <v>-1.330987755369641</v>
+        <v>-2.277530880219927</v>
       </c>
       <c r="G96">
-        <v>1.575411328923421</v>
+        <v>-1.667850682807619</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.525848433888095</v>
       </c>
       <c r="E97">
-        <v>-36.08348752110503</v>
+        <v>-38.80916923361081</v>
       </c>
       <c r="F97">
-        <v>-1.398532833393913</v>
+        <v>-1.617638496536591</v>
       </c>
       <c r="G97">
-        <v>0.6473495451718325</v>
+        <v>-2.57854865520573</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.257202882328296</v>
       </c>
       <c r="E98">
-        <v>-39.07251131834186</v>
+        <v>-40.71883125111941</v>
       </c>
       <c r="F98">
-        <v>-1.265191360932679</v>
+        <v>-2.507797137380523</v>
       </c>
       <c r="G98">
-        <v>-0.1036212260475221</v>
+        <v>-1.847914565234118</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.010700950324929</v>
       </c>
       <c r="E99">
-        <v>-40.75522433248205</v>
+        <v>-42.04975881892174</v>
       </c>
       <c r="F99">
-        <v>-1.330403756350668</v>
+        <v>-2.440067333425427</v>
       </c>
       <c r="G99">
-        <v>-0.5391565971940394</v>
+        <v>-1.809945918444217</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.803091409482956</v>
       </c>
       <c r="E100">
-        <v>-41.59633403771873</v>
+        <v>-44.80621151230964</v>
       </c>
       <c r="F100">
-        <v>-1.25311873440428</v>
+        <v>-2.50552078375763</v>
       </c>
       <c r="G100">
-        <v>-0.1054751315495139</v>
+        <v>-2.705935137011346</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.557254765033333</v>
       </c>
       <c r="E101">
-        <v>-43.99188546659133</v>
+        <v>-46.34370315773485</v>
       </c>
       <c r="F101">
-        <v>-1.142156435697077</v>
+        <v>-2.308486970062545</v>
       </c>
       <c r="G101">
-        <v>0.2083745172100124</v>
+        <v>-2.463470781715124</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.364836803782243</v>
       </c>
       <c r="E102">
-        <v>-46.75357534016909</v>
+        <v>-48.81559560142876</v>
       </c>
       <c r="F102">
-        <v>-1.544705716924511</v>
+        <v>-2.185635114022961</v>
       </c>
       <c r="G102">
-        <v>-1.376036025157481</v>
+        <v>-2.409760490885988</v>
       </c>
     </row>
   </sheetData>
